--- a/Sevastopol AI Архив событий.xlsx
+++ b/Sevastopol AI Архив событий.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -570,7 +570,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Концерты</t>
+          <t>Театр</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -580,95 +580,95 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Дом офицеров флота (Ленина, 9)</t>
+          <t>Театр им. Луначарского (пр. Нахимова, 6)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Театрально-музыкально-поэтический диалог «Ритм и рифма»</t>
+          <t>Спектакль «Мастер и Маргарита»</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>✔️ Вход свободный</t>
+          <t>✔️ Булгаков, 18+
+✔️ Начало в 17:00</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://afisha.sevastopol.press/event/-891</t>
+          <t>https://quicktickets.ru/sevastopol-teatr-lunacharskogo</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://afisha.sevastopol.press/event/-891</t>
+          <t>https://quicktickets.ru/sevastopol-teatr-lunacharskogo</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Концерты</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>19.09.2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Дом офицеров флота (Ленина, 9)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Театрально-музыкально-поэтический диалог «Ритм и рифма»</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>✔️ Вход свободный</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://afisha.sevastopol.press/event/-891</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://afisha.sevastopol.press/event/-891</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Театр</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>19.09.2026</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Театр им. Луначарского (пр. Нахимова, 6)</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Экскурсия по театру</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>✔️ Закулисье главного театра города, 6+
 ✔️ Начало в 13:00</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>https://quicktickets.ru/sevastopol-teatr-lunacharskogo</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://quicktickets.ru/sevastopol-teatr-lunacharskogo</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Театр</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>19.09.2026</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Театр им. Луначарского (пр. Нахимова, 6)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Спектакль «Мастер и Маргарита»</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>✔️ Булгаков, 18+
-✔️ Начало в 17:00</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>https://quicktickets.ru/sevastopol-teatr-lunacharskogo</t>
@@ -693,66 +693,66 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>Экопространство «Али-Баир», Байдарская долина</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>«Кино на струнах» с дуэтом виолончелей</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>✔️ 1200 ₽
+✔️ Саундтреки из кино в горах Байдарской долины</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>https://afisha.sevastopol.press/event/-888</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://afisha.sevastopol.press/event/-888</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Концерты</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>20.09.2026</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>Дом офицеров флота (Ленина, 9)</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Гала-концерт фестиваля фламенко «Sobre las Olas»</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>✔️ Вход свободный
 ✔️ Испанское фламенко на сцене ДОФ</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>https://afisha.sevastopol.press/event/-890</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>https://afisha.sevastopol.press/event/-890</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Концерты</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>20.09.2026</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Экопространство «Али-Баир», Байдарская долина</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>«Кино на струнах» с дуэтом виолончелей</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>✔️ 1200 ₽
-✔️ Саундтреки из кино в горах Байдарской долины</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>https://afisha.sevastopol.press/event/-888</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://afisha.sevastopol.press/event/-888</t>
         </is>
       </c>
     </row>
@@ -943,6 +943,158 @@
       <c r="G14" t="inlineStr">
         <is>
           <t>https://quicktickets.ru/sevastopol-teatr-lunacharskogo</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Театр</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>26.09.2026</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Театр им. Луначарского (пр. Нахимова, 6)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Спектакль «Бесы»</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>✔️ Достоевский, 16+
+✔️ Начало в 18:00</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>https://quicktickets.ru/sevastopol-teatr-lunacharskogo</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://quicktickets.ru/sevastopol-teatr-lunacharskogo</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Театр</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>27.09.2026</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Театр им. Луначарского (пр. Нахимова, 6)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Спектакль «Доктор Живаго»</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>✔️ Пастернак, драма 16+
+✔️ Начало в 17:00</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>https://quicktickets.ru/sevastopol-teatr-lunacharskogo</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://quicktickets.ru/sevastopol-teatr-lunacharskogo</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Театр</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>03.10.2026</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Театр им. Луначарского (пр. Нахимова, 6)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Спектакль «Три сестры»</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>✔️ Чехов, 16+
+✔️ Начало в 18:00</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>https://quicktickets.ru/sevastopol-teatr-lunacharskogo</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://quicktickets.ru/sevastopol-teatr-lunacharskogo</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Концерты</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>11.10.2026</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Скельская пещера</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>«Инструментальное путешествие» в Скельской пещере</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>✔️ 1500 ₽, 6+
+✔️ Концерт в пещере с уникальной акустикой</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>https://afisha.sevastopol.press/event/-889</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://afisha.sevastopol.press/event/-889</t>
         </is>
       </c>
     </row>
